--- a/www/terminologies/ValueSet-jdv-j408-orientation-ms.xlsx
+++ b/www/terminologies/ValueSet-jdv-j408-orientation-ms.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="45">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260601120000</t>
+    <t>20260928120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:00:00.000+00:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -110,9 +110,6 @@
     <t>=</t>
   </si>
   <si>
-    <t>active</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -152,7 +149,7 @@
     <t>Unité d'enseignement en maternelle plan autisme</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R278-FinessConvention/FHIR/TRE-R278-FinessConvention</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r395-engagement</t>
   </si>
 </sst>
 </file>
@@ -442,23 +439,23 @@
         <v>30</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>33</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -477,7 +474,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>22</v>
@@ -485,34 +482,34 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>36</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -531,7 +528,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>22</v>
@@ -539,34 +536,34 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>41</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>43</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
